--- a/ipo-analysis/companies/bombay-coated-and-special-steels-ltd/BOMBAY_COATED_AND_SPECIA_02_Anchor_QIB.xlsx
+++ b/ipo-analysis/companies/bombay-coated-and-special-steels-ltd/BOMBAY_COATED_AND_SPECIA_02_Anchor_QIB.xlsx
@@ -1298,7 +1298,9 @@
           <t>Allotment date (basis of allotment)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="n"/>
+      <c r="C32" s="16" t="n">
+        <v>46329</v>
+      </c>
       <c r="D32" s="9" t="inlineStr"/>
       <c r="E32" s="10" t="inlineStr">
         <is>
@@ -1312,7 +1314,9 @@
           <t>Listing date</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n"/>
+      <c r="C33" s="16" t="n">
+        <v>46331</v>
+      </c>
       <c r="D33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2576,7 +2580,7 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>pp. 28-29, 94; six months - confirm in RHP</t>
+          <t>p. 106; six months</t>
         </is>
       </c>
     </row>
@@ -2587,10 +2591,10 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>271.59</v>
+        <v>270.35</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>365</v>
+        <v>180</v>
       </c>
       <c r="E12" s="24">
         <f>'Inputs'!$C$32+D12</f>
@@ -2614,7 +2618,7 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>one year if the lease buy-out counts as capex, else six months - confirm in RHP</t>
+          <t>p. 106; six months from allotment</t>
         </is>
       </c>
     </row>
@@ -2625,10 +2629,10 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>124.41</v>
+        <v>125.65</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>1095</v>
+        <v>540</v>
       </c>
       <c r="E13" s="24">
         <f>'Inputs'!$C$32+D13</f>
@@ -2652,7 +2656,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>three years if capex, else 18 months - confirm in RHP</t>
+          <t>p. 106; 18 months from allotment</t>
         </is>
       </c>
     </row>
